--- a/example_data/reference_example.xlsx
+++ b/example_data/reference_example.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\beke\Documents\MassmatchR_v0.9.21\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\beke\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8518902-14AD-43A7-812E-2806D8357483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B434374-5BB4-414D-904C-36BAA20485B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10635" yWindow="4140" windowWidth="35100" windowHeight="15345" xr2:uid="{1099D031-B553-4520-8B6C-2C52DF8BBF8E}"/>
+    <workbookView xWindow="5415" yWindow="5415" windowWidth="57600" windowHeight="15345" xr2:uid="{1099D031-B553-4520-8B6C-2C52DF8BBF8E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hárok1" sheetId="1" r:id="rId1"/>
@@ -1479,9 +1479,7 @@
       <c r="C7" s="1">
         <v>1579.7826</v>
       </c>
-      <c r="D7" s="1">
-        <v>1579.7826</v>
-      </c>
+      <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -1504,9 +1502,7 @@
       <c r="C9" s="1">
         <v>1620.8090999999999</v>
       </c>
-      <c r="D9" s="1">
-        <v>1620.8090999999999</v>
-      </c>
+      <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -1518,9 +1514,7 @@
       <c r="C10" s="1">
         <v>1661.8357000000001</v>
       </c>
-      <c r="D10" s="1">
-        <v>1661.8357000000001</v>
-      </c>
+      <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -1543,9 +1537,7 @@
       <c r="C12" s="1">
         <v>1783.8824</v>
       </c>
-      <c r="D12" s="1">
-        <v>1783.8824</v>
-      </c>
+      <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -1590,9 +1582,7 @@
       <c r="C16" s="1">
         <v>1835.9249</v>
       </c>
-      <c r="D16" s="1">
-        <v>1835.9249</v>
-      </c>
+      <c r="D16" s="1"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
@@ -1604,9 +1594,7 @@
       <c r="C17" s="1">
         <v>1865.9355</v>
       </c>
-      <c r="D17" s="1">
-        <v>1865.9355</v>
-      </c>
+      <c r="D17" s="1"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
@@ -1618,9 +1606,7 @@
       <c r="C18" s="1">
         <v>1906.962</v>
       </c>
-      <c r="D18" s="1">
-        <v>1906.962</v>
-      </c>
+      <c r="D18" s="1"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
@@ -1643,9 +1629,7 @@
       <c r="C20" s="1">
         <v>1987.9822999999999</v>
       </c>
-      <c r="D20" s="1">
-        <v>1987.9820999999999</v>
-      </c>
+      <c r="D20" s="1"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
@@ -1712,9 +1696,7 @@
       <c r="C26" s="1">
         <v>2040.0246999999999</v>
       </c>
-      <c r="D26" s="1">
-        <v>2040.0246999999999</v>
-      </c>
+      <c r="D26" s="1"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
@@ -1726,9 +1708,7 @@
       <c r="C27" s="1">
         <v>2070.0351999999998</v>
       </c>
-      <c r="D27" s="1">
-        <v>2070.0351999999998</v>
-      </c>
+      <c r="D27" s="1"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
@@ -1740,9 +1720,7 @@
       <c r="C28" s="1">
         <v>2081.0511999999999</v>
       </c>
-      <c r="D28" s="1">
-        <v>2081.0511999999999</v>
-      </c>
+      <c r="D28" s="1"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
@@ -1776,9 +1754,7 @@
       <c r="C31" s="1">
         <v>2156.0720000000001</v>
       </c>
-      <c r="D31" s="1">
-        <v>2156.0720000000001</v>
-      </c>
+      <c r="D31" s="1"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
@@ -1790,9 +1766,7 @@
       <c r="C32" s="1">
         <v>2192.0819000000001</v>
       </c>
-      <c r="D32" s="1">
-        <v>2192.0819000000001</v>
-      </c>
+      <c r="D32" s="1"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
@@ -1815,9 +1789,7 @@
       <c r="C34" s="1">
         <v>2186.0826000000002</v>
       </c>
-      <c r="D34" s="1">
-        <v>2186.0826000000002</v>
-      </c>
+      <c r="D34" s="1"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
@@ -1862,9 +1834,7 @@
       <c r="C38" s="1">
         <v>2227.1091000000001</v>
       </c>
-      <c r="D38" s="1">
-        <v>2227.1091000000001</v>
-      </c>
+      <c r="D38" s="1"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
@@ -1887,9 +1857,7 @@
       <c r="C40" s="1">
         <v>2244.1244999999999</v>
       </c>
-      <c r="D40" s="1">
-        <v>2244.1244999999999</v>
-      </c>
+      <c r="D40" s="1"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
@@ -1923,9 +1891,7 @@
       <c r="C43" s="1">
         <v>2285.1509999999998</v>
       </c>
-      <c r="D43" s="1">
-        <v>2285.1509999999998</v>
-      </c>
+      <c r="D43" s="1"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
@@ -1992,9 +1958,7 @@
       <c r="C49" s="1">
         <v>2396.1817000000001</v>
       </c>
-      <c r="D49" s="1">
-        <v>2396.1817000000001</v>
-      </c>
+      <c r="D49" s="1"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
@@ -2017,9 +1981,7 @@
       <c r="C51" s="1">
         <v>2390.1824000000001</v>
       </c>
-      <c r="D51" s="1">
-        <v>2390.1824000000001</v>
-      </c>
+      <c r="D51" s="1"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
@@ -2042,9 +2004,7 @@
       <c r="C53" s="1">
         <v>2401.1983</v>
       </c>
-      <c r="D53" s="1">
-        <v>2401.1983</v>
-      </c>
+      <c r="D53" s="1"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
@@ -2078,9 +2038,7 @@
       <c r="C56" s="1">
         <v>2431.2089000000001</v>
       </c>
-      <c r="D56" s="1">
-        <v>2431.2089000000001</v>
-      </c>
+      <c r="D56" s="1"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
@@ -2279,9 +2237,7 @@
       <c r="C74" s="1">
         <v>2605.2981</v>
       </c>
-      <c r="D74" s="1">
-        <v>2605.2981</v>
-      </c>
+      <c r="D74" s="1"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
@@ -2381,9 +2337,7 @@
       <c r="C83" s="1">
         <v>2676.3352</v>
       </c>
-      <c r="D83" s="1">
-        <v>2676.3352</v>
-      </c>
+      <c r="D83" s="1"/>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
@@ -2538,9 +2492,7 @@
       <c r="C97" s="1">
         <v>2792.3825999999999</v>
       </c>
-      <c r="D97" s="1">
-        <v>2792.3825999999999</v>
-      </c>
+      <c r="D97" s="1"/>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
@@ -2651,9 +2603,7 @@
       <c r="C107" s="1">
         <v>2850.4243999999999</v>
       </c>
-      <c r="D107" s="1">
-        <v>2850.4243999999999</v>
-      </c>
+      <c r="D107" s="1"/>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
@@ -2676,9 +2626,7 @@
       <c r="C109" s="1">
         <v>2880.4349999999999</v>
       </c>
-      <c r="D109" s="1">
-        <v>2880.4349999999999</v>
-      </c>
+      <c r="D109" s="1"/>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
@@ -2866,9 +2814,7 @@
       <c r="C126" s="1">
         <v>2996.4823999999999</v>
       </c>
-      <c r="D126" s="1">
-        <v>2996.4823999999999</v>
-      </c>
+      <c r="D126" s="1"/>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
@@ -2979,9 +2925,7 @@
       <c r="C136" s="1">
         <v>3054.5241999999998</v>
       </c>
-      <c r="D136" s="1">
-        <v>3054.5241999999998</v>
-      </c>
+      <c r="D136" s="1"/>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
@@ -3257,9 +3201,7 @@
       <c r="C161" s="1">
         <v>3211.5981000000002</v>
       </c>
-      <c r="D161" s="1">
-        <v>3211.5981000000002</v>
-      </c>
+      <c r="D161" s="1"/>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
@@ -3293,9 +3235,7 @@
       <c r="C164" s="1">
         <v>3241.6087000000002</v>
       </c>
-      <c r="D164" s="1">
-        <v>3241.6087000000002</v>
-      </c>
+      <c r="D164" s="1"/>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
@@ -3604,9 +3544,7 @@
       <c r="C192" s="1">
         <v>3415.6979000000001</v>
       </c>
-      <c r="D192" s="1">
-        <v>3415.6979000000001</v>
-      </c>
+      <c r="D192" s="1"/>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
@@ -3882,9 +3820,7 @@
       <c r="C217" s="1">
         <v>3602.7822999999999</v>
       </c>
-      <c r="D217" s="1">
-        <v>3602.7822999999999</v>
-      </c>
+      <c r="D217" s="1"/>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
@@ -4006,9 +3942,7 @@
       <c r="C228" s="1">
         <v>3690.8348000000001</v>
       </c>
-      <c r="D228" s="1">
-        <v>3690.8348000000001</v>
-      </c>
+      <c r="D228" s="1"/>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
@@ -4163,9 +4097,7 @@
       <c r="C242" s="1">
         <v>3776.8715999999999</v>
       </c>
-      <c r="D242" s="1">
-        <v>3776.8715999999999</v>
-      </c>
+      <c r="D242" s="1"/>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
